--- a/artfynd/A 29088-2023 artfynd.xlsx
+++ b/artfynd/A 29088-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29088-2023 artfynd.xlsx
+++ b/artfynd/A 29088-2023 artfynd.xlsx
@@ -6241,10 +6241,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118641453</v>
+        <v>118640943</v>
       </c>
       <c r="B53" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6257,34 +6257,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>715142</v>
+        <v>715563</v>
       </c>
       <c r="R53" t="n">
-        <v>7303469</v>
+        <v>7303066</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6325,32 +6328,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118637560</v>
+        <v>118637563</v>
       </c>
       <c r="B54" t="n">
-        <v>86224</v>
+        <v>78220</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6363,21 +6363,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>249254</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mospindling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius areni-silvae</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brandrud) Brandrud</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6387,10 +6387,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715218</v>
+        <v>715432</v>
       </c>
       <c r="R54" t="n">
-        <v>7302983</v>
+        <v>7303244</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6453,10 +6453,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118637572</v>
+        <v>118639963</v>
       </c>
       <c r="B55" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6469,21 +6469,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>715538</v>
+        <v>715505</v>
       </c>
       <c r="R55" t="n">
-        <v>7303121</v>
+        <v>7302998</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6543,12 +6543,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6559,10 +6559,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118639925</v>
+        <v>118637572</v>
       </c>
       <c r="B56" t="n">
-        <v>56502</v>
+        <v>90522</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6571,25 +6571,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6599,13 +6599,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>715132</v>
+        <v>715538</v>
       </c>
       <c r="R56" t="n">
-        <v>7303473</v>
+        <v>7303121</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6635,11 +6635,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6654,12 +6649,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6670,10 +6665,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118640943</v>
+        <v>118639925</v>
       </c>
       <c r="B57" t="n">
-        <v>78484</v>
+        <v>56502</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6682,44 +6677,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>715563</v>
+        <v>715132</v>
       </c>
       <c r="R57" t="n">
-        <v>7303066</v>
+        <v>7303473</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6751,35 +6743,43 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118637563</v>
+        <v>118637564</v>
       </c>
       <c r="B58" t="n">
-        <v>78220</v>
+        <v>78566</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6792,21 +6792,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715432</v>
+        <v>715481</v>
       </c>
       <c r="R58" t="n">
-        <v>7303244</v>
+        <v>7302986</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6882,10 +6882,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118639963</v>
+        <v>118642110</v>
       </c>
       <c r="B59" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6898,21 +6898,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6922,13 +6922,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>715505</v>
+        <v>715561</v>
       </c>
       <c r="R59" t="n">
-        <v>7302998</v>
+        <v>7303003</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6972,12 +6972,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6988,10 +6988,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118637564</v>
+        <v>118639947</v>
       </c>
       <c r="B60" t="n">
-        <v>78566</v>
+        <v>78221</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7004,21 +7004,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7028,13 +7028,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715481</v>
+        <v>715413</v>
       </c>
       <c r="R60" t="n">
-        <v>7302986</v>
+        <v>7302983</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7078,12 +7078,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7094,10 +7094,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118642110</v>
+        <v>118641453</v>
       </c>
       <c r="B61" t="n">
-        <v>90504</v>
+        <v>79073</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7110,21 +7110,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715561</v>
+        <v>715142</v>
       </c>
       <c r="R61" t="n">
-        <v>7303003</v>
+        <v>7303469</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7184,12 +7184,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7200,10 +7200,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118639947</v>
+        <v>118637560</v>
       </c>
       <c r="B62" t="n">
-        <v>78221</v>
+        <v>86224</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7216,21 +7216,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>249254</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mospindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cortinarius areni-silvae</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brandrud) Brandrud</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7240,13 +7240,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715413</v>
+        <v>715218</v>
       </c>
       <c r="R62" t="n">
         <v>7302983</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7290,12 +7290,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -8716,7 +8716,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118640700</v>
+        <v>118638435</v>
       </c>
       <c r="B76" t="n">
         <v>79102</v>
@@ -8756,13 +8756,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715069</v>
+        <v>715205</v>
       </c>
       <c r="R76" t="n">
-        <v>7302903</v>
+        <v>7303041</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8806,26 +8806,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118639959</v>
+        <v>118639919</v>
       </c>
       <c r="B77" t="n">
-        <v>78484</v>
+        <v>104925</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8834,25 +8830,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8862,10 +8858,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715226</v>
+        <v>715338</v>
       </c>
       <c r="R77" t="n">
-        <v>7303445</v>
+        <v>7303350</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8928,10 +8924,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118641285</v>
+        <v>118638437</v>
       </c>
       <c r="B78" t="n">
-        <v>78220</v>
+        <v>97867</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8940,41 +8936,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>715438</v>
+        <v>715347</v>
       </c>
       <c r="R78" t="n">
-        <v>7303256</v>
+        <v>7302995</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9004,47 +8997,40 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118638435</v>
+        <v>118640700</v>
       </c>
       <c r="B79" t="n">
         <v>79102</v>
@@ -9084,13 +9070,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>715205</v>
+        <v>715069</v>
       </c>
       <c r="R79" t="n">
-        <v>7303041</v>
+        <v>7302903</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9134,22 +9120,26 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118638437</v>
+        <v>118639959</v>
       </c>
       <c r="B80" t="n">
-        <v>97867</v>
+        <v>78484</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9158,25 +9148,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9186,13 +9176,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>715347</v>
+        <v>715226</v>
       </c>
       <c r="R80" t="n">
-        <v>7302995</v>
+        <v>7303445</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9236,12 +9226,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9252,10 +9242,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118641293</v>
+        <v>118641285</v>
       </c>
       <c r="B81" t="n">
-        <v>78221</v>
+        <v>78220</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9268,21 +9258,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9585,10 +9575,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118639919</v>
+        <v>118641293</v>
       </c>
       <c r="B84" t="n">
-        <v>104925</v>
+        <v>78221</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9597,41 +9587,44 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221725</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715338</v>
+        <v>715438</v>
       </c>
       <c r="R84" t="n">
-        <v>7303350</v>
+        <v>7303256</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9658,43 +9651,50 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118640654</v>
+        <v>118640710</v>
       </c>
       <c r="B85" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9707,40 +9707,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715115</v>
+        <v>715150</v>
       </c>
       <c r="R85" t="n">
-        <v>7302894</v>
+        <v>7303439</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9778,29 +9775,32 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118641466</v>
+        <v>118639921</v>
       </c>
       <c r="B86" t="n">
-        <v>78484</v>
+        <v>90430</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9813,21 +9813,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9837,13 +9837,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715566</v>
+        <v>715119</v>
       </c>
       <c r="R86" t="n">
-        <v>7303083</v>
+        <v>7302948</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9887,12 +9887,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9903,7 +9903,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118638450</v>
+        <v>118640654</v>
       </c>
       <c r="B87" t="n">
         <v>78484</v>
@@ -9937,16 +9937,19 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715585</v>
+        <v>715115</v>
       </c>
       <c r="R87" t="n">
-        <v>7303032</v>
+        <v>7302894</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9987,32 +9990,29 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118640691</v>
+        <v>118641466</v>
       </c>
       <c r="B88" t="n">
-        <v>95394</v>
+        <v>78484</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10025,21 +10025,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10049,13 +10049,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715323</v>
+        <v>715566</v>
       </c>
       <c r="R88" t="n">
-        <v>7303053</v>
+        <v>7303083</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10099,12 +10099,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10115,10 +10115,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118639921</v>
+        <v>118638450</v>
       </c>
       <c r="B89" t="n">
-        <v>90430</v>
+        <v>78484</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10131,21 +10131,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10155,13 +10155,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715119</v>
+        <v>715585</v>
       </c>
       <c r="R89" t="n">
-        <v>7302948</v>
+        <v>7303032</v>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10205,12 +10205,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10539,10 +10539,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118640710</v>
+        <v>118640691</v>
       </c>
       <c r="B93" t="n">
-        <v>78221</v>
+        <v>95394</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10555,21 +10555,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715150</v>
+        <v>715323</v>
       </c>
       <c r="R93" t="n">
-        <v>7303439</v>
+        <v>7303053</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -11197,10 +11197,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118640750</v>
+        <v>118640749</v>
       </c>
       <c r="B99" t="n">
-        <v>90469</v>
+        <v>78566</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11209,25 +11209,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5447</v>
+        <v>864</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11303,10 +11303,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118639920</v>
+        <v>118639953</v>
       </c>
       <c r="B100" t="n">
-        <v>90430</v>
+        <v>90654</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11315,25 +11315,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715266</v>
+        <v>715480</v>
       </c>
       <c r="R100" t="n">
-        <v>7303459</v>
+        <v>7302982</v>
       </c>
       <c r="S100" t="n">
         <v>1</v>
@@ -11409,10 +11409,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118640850</v>
+        <v>118642121</v>
       </c>
       <c r="B101" t="n">
-        <v>78484</v>
+        <v>90518</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11425,37 +11425,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715385</v>
+        <v>715581</v>
       </c>
       <c r="R101" t="n">
-        <v>7303019</v>
+        <v>7303107</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11496,29 +11493,32 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118639962</v>
+        <v>118639924</v>
       </c>
       <c r="B102" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11531,21 +11531,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11555,10 +11555,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>715598</v>
+        <v>715338</v>
       </c>
       <c r="R102" t="n">
-        <v>7302991</v>
+        <v>7303353</v>
       </c>
       <c r="S102" t="n">
         <v>1</v>
@@ -11621,10 +11621,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118640749</v>
+        <v>118640750</v>
       </c>
       <c r="B103" t="n">
-        <v>78566</v>
+        <v>90469</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11633,25 +11633,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>864</v>
+        <v>5447</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11727,10 +11727,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118639953</v>
+        <v>118639920</v>
       </c>
       <c r="B104" t="n">
-        <v>90654</v>
+        <v>90430</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11739,25 +11739,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11767,10 +11767,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>715480</v>
+        <v>715266</v>
       </c>
       <c r="R104" t="n">
-        <v>7302982</v>
+        <v>7303459</v>
       </c>
       <c r="S104" t="n">
         <v>1</v>
@@ -11833,10 +11833,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118642121</v>
+        <v>118640850</v>
       </c>
       <c r="B105" t="n">
-        <v>90518</v>
+        <v>78484</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11849,34 +11849,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>715581</v>
+        <v>715385</v>
       </c>
       <c r="R105" t="n">
-        <v>7303107</v>
+        <v>7303019</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11917,32 +11920,29 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118639924</v>
+        <v>118639962</v>
       </c>
       <c r="B106" t="n">
-        <v>90504</v>
+        <v>78484</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11955,21 +11955,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11979,10 +11979,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>715338</v>
+        <v>715598</v>
       </c>
       <c r="R106" t="n">
-        <v>7303353</v>
+        <v>7302991</v>
       </c>
       <c r="S106" t="n">
         <v>1</v>
@@ -12151,10 +12151,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118640727</v>
+        <v>118639261</v>
       </c>
       <c r="B108" t="n">
-        <v>77868</v>
+        <v>78566</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12167,37 +12167,40 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6437</v>
+        <v>864</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>715320</v>
+        <v>715520</v>
       </c>
       <c r="R108" t="n">
-        <v>7303018</v>
+        <v>7303163</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12235,18 +12238,19 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12257,10 +12261,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118640741</v>
+        <v>118639952</v>
       </c>
       <c r="B109" t="n">
-        <v>78484</v>
+        <v>90518</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12273,21 +12277,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12297,13 +12301,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>715288</v>
+        <v>715088</v>
       </c>
       <c r="R109" t="n">
-        <v>7302949</v>
+        <v>7302934</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12347,12 +12351,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12363,10 +12367,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118639057</v>
+        <v>118637565</v>
       </c>
       <c r="B110" t="n">
-        <v>74596</v>
+        <v>91116</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12379,40 +12383,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6440</v>
+        <v>5454</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>715250</v>
+        <v>715247</v>
       </c>
       <c r="R110" t="n">
-        <v>7303027</v>
+        <v>7302980</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12450,19 +12451,18 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12473,10 +12473,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118642123</v>
+        <v>118640727</v>
       </c>
       <c r="B111" t="n">
-        <v>5166</v>
+        <v>77868</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12485,25 +12485,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100526</v>
+        <v>6437</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12513,13 +12513,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>715473</v>
+        <v>715320</v>
       </c>
       <c r="R111" t="n">
-        <v>7302975</v>
+        <v>7303018</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12563,12 +12563,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12579,10 +12579,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118641187</v>
+        <v>118640741</v>
       </c>
       <c r="B112" t="n">
-        <v>57443</v>
+        <v>78484</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12595,46 +12595,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>715514</v>
+        <v>715288</v>
       </c>
       <c r="R112" t="n">
-        <v>7303116</v>
+        <v>7302949</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12664,19 +12652,9 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12691,22 +12669,26 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr"/>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118637558</v>
+        <v>118639057</v>
       </c>
       <c r="B113" t="n">
-        <v>78221</v>
+        <v>74596</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12719,37 +12701,40 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715556</v>
+        <v>715250</v>
       </c>
       <c r="R113" t="n">
-        <v>7303103</v>
+        <v>7303027</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12787,18 +12772,19 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12809,10 +12795,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118637565</v>
+        <v>118642123</v>
       </c>
       <c r="B114" t="n">
-        <v>91116</v>
+        <v>5166</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12821,25 +12807,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5454</v>
+        <v>100526</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12849,10 +12835,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>715247</v>
+        <v>715473</v>
       </c>
       <c r="R114" t="n">
-        <v>7302980</v>
+        <v>7302975</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12899,12 +12885,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12915,10 +12901,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118639261</v>
+        <v>118641187</v>
       </c>
       <c r="B115" t="n">
-        <v>78566</v>
+        <v>57443</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12931,26 +12917,35 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>864</v>
+        <v>103021</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12958,13 +12953,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>715520</v>
+        <v>715514</v>
       </c>
       <c r="R115" t="n">
-        <v>7303163</v>
+        <v>7303116</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12991,44 +12986,49 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118639952</v>
+        <v>118641461</v>
       </c>
       <c r="B116" t="n">
-        <v>90518</v>
+        <v>96807</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13037,25 +13037,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1204</v>
+        <v>221941</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13065,13 +13065,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>715088</v>
+        <v>715070</v>
       </c>
       <c r="R116" t="n">
-        <v>7302934</v>
+        <v>7302926</v>
       </c>
       <c r="S116" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13115,12 +13115,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -13131,7 +13131,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118641461</v>
+        <v>118637548</v>
       </c>
       <c r="B117" t="n">
         <v>96807</v>
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>715070</v>
+        <v>715528</v>
       </c>
       <c r="R117" t="n">
-        <v>7302926</v>
+        <v>7303144</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13221,12 +13221,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -13237,10 +13237,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118637548</v>
+        <v>118637558</v>
       </c>
       <c r="B118" t="n">
-        <v>96807</v>
+        <v>78221</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13249,25 +13249,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13277,10 +13277,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>715528</v>
+        <v>715556</v>
       </c>
       <c r="R118" t="n">
-        <v>7303144</v>
+        <v>7303103</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15808,10 +15808,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118637536</v>
+        <v>118640699</v>
       </c>
       <c r="B142" t="n">
-        <v>97867</v>
+        <v>79102</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15820,25 +15820,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15848,13 +15848,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>715540</v>
+        <v>715120</v>
       </c>
       <c r="R142" t="n">
-        <v>7303127</v>
+        <v>7302906</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15898,12 +15898,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15914,10 +15914,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118641310</v>
+        <v>118640694</v>
       </c>
       <c r="B143" t="n">
-        <v>97867</v>
+        <v>79102</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15926,49 +15926,41 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>715194</v>
+        <v>715510</v>
       </c>
       <c r="R143" t="n">
-        <v>7303422</v>
+        <v>7302980</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15995,50 +15987,43 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY143" t="inlineStr"/>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118640707</v>
+        <v>118637577</v>
       </c>
       <c r="B144" t="n">
-        <v>96807</v>
+        <v>78484</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16047,25 +16032,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16075,13 +16060,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>715323</v>
+        <v>715544</v>
       </c>
       <c r="R144" t="n">
-        <v>7303053</v>
+        <v>7303055</v>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16125,12 +16110,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -16141,10 +16126,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118642118</v>
+        <v>118638447</v>
       </c>
       <c r="B145" t="n">
-        <v>78221</v>
+        <v>78566</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16157,21 +16142,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16181,10 +16166,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>715332</v>
+        <v>715583</v>
       </c>
       <c r="R145" t="n">
-        <v>7303306</v>
+        <v>7303046</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16231,12 +16216,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -16247,10 +16232,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118642116</v>
+        <v>118640758</v>
       </c>
       <c r="B146" t="n">
-        <v>57306</v>
+        <v>82263</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16263,42 +16248,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>715240</v>
+        <v>715583</v>
       </c>
       <c r="R146" t="n">
-        <v>7303369</v>
+        <v>7303009</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16333,11 +16310,6 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
@@ -16350,12 +16322,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -16366,10 +16338,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118638447</v>
+        <v>118642116</v>
       </c>
       <c r="B147" t="n">
-        <v>78566</v>
+        <v>57306</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16382,34 +16354,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>715583</v>
+        <v>715240</v>
       </c>
       <c r="R147" t="n">
-        <v>7303046</v>
+        <v>7303369</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16444,6 +16424,11 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
@@ -16456,12 +16441,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -16472,10 +16457,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118640758</v>
+        <v>118637536</v>
       </c>
       <c r="B148" t="n">
-        <v>82263</v>
+        <v>97867</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16484,25 +16469,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16512,10 +16497,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>715583</v>
+        <v>715540</v>
       </c>
       <c r="R148" t="n">
-        <v>7303009</v>
+        <v>7303127</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16562,12 +16547,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -16578,10 +16563,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118640699</v>
+        <v>118641310</v>
       </c>
       <c r="B149" t="n">
-        <v>79102</v>
+        <v>97867</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16590,41 +16575,49 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>715120</v>
+        <v>715194</v>
       </c>
       <c r="R149" t="n">
-        <v>7302906</v>
+        <v>7303422</v>
       </c>
       <c r="S149" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16651,43 +16644,50 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118640694</v>
+        <v>118640707</v>
       </c>
       <c r="B150" t="n">
-        <v>79102</v>
+        <v>96807</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16696,25 +16696,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16724,10 +16724,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>715510</v>
+        <v>715323</v>
       </c>
       <c r="R150" t="n">
-        <v>7302980</v>
+        <v>7303053</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -16790,10 +16790,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118637577</v>
+        <v>118642118</v>
       </c>
       <c r="B151" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16806,21 +16806,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16830,10 +16830,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>715544</v>
+        <v>715332</v>
       </c>
       <c r="R151" t="n">
-        <v>7303055</v>
+        <v>7303306</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16880,12 +16880,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -17638,10 +17638,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118639934</v>
+        <v>118640752</v>
       </c>
       <c r="B159" t="n">
-        <v>79594</v>
+        <v>82263</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17650,25 +17650,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17678,13 +17678,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>715479</v>
+        <v>715548</v>
       </c>
       <c r="R159" t="n">
-        <v>7303167</v>
+        <v>7303162</v>
       </c>
       <c r="S159" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17728,12 +17728,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -17744,10 +17744,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>118641463</v>
+        <v>118640755</v>
       </c>
       <c r="B160" t="n">
-        <v>79601</v>
+        <v>57306</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17756,25 +17756,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17784,10 +17784,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>715474</v>
+        <v>715615</v>
       </c>
       <c r="R160" t="n">
-        <v>7303165</v>
+        <v>7303127</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17822,6 +17822,11 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
@@ -17834,12 +17839,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -17850,10 +17855,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>118640755</v>
+        <v>118639951</v>
       </c>
       <c r="B161" t="n">
-        <v>57306</v>
+        <v>57401</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17862,20 +17867,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -17890,13 +17895,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>715615</v>
+        <v>715118</v>
       </c>
       <c r="R161" t="n">
-        <v>7303127</v>
+        <v>7302948</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17926,11 +17931,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17945,12 +17945,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -17961,10 +17961,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>118639951</v>
+        <v>118639934</v>
       </c>
       <c r="B162" t="n">
-        <v>57401</v>
+        <v>79594</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17977,21 +17977,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18001,10 +18001,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>715118</v>
+        <v>715479</v>
       </c>
       <c r="R162" t="n">
-        <v>7302948</v>
+        <v>7303167</v>
       </c>
       <c r="S162" t="n">
         <v>1</v>
@@ -18067,10 +18067,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>118639937</v>
+        <v>118641463</v>
       </c>
       <c r="B163" t="n">
-        <v>97867</v>
+        <v>79601</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18083,21 +18083,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18107,13 +18107,13 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>715562</v>
+        <v>715474</v>
       </c>
       <c r="R163" t="n">
-        <v>7303104</v>
+        <v>7303165</v>
       </c>
       <c r="S163" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18157,12 +18157,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -18173,7 +18173,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>118641455</v>
+        <v>118639937</v>
       </c>
       <c r="B164" t="n">
         <v>97867</v>
@@ -18213,13 +18213,13 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>715530</v>
+        <v>715562</v>
       </c>
       <c r="R164" t="n">
-        <v>7303171</v>
+        <v>7303104</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18263,12 +18263,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -18279,10 +18279,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>118640713</v>
+        <v>118641455</v>
       </c>
       <c r="B165" t="n">
-        <v>78221</v>
+        <v>97867</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18291,25 +18291,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18319,13 +18319,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>715322</v>
+        <v>715530</v>
       </c>
       <c r="R165" t="n">
-        <v>7303020</v>
+        <v>7303171</v>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18369,12 +18369,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -18385,10 +18385,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>118640701</v>
+        <v>118640713</v>
       </c>
       <c r="B166" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18401,21 +18401,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18425,10 +18425,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>715173</v>
+        <v>715322</v>
       </c>
       <c r="R166" t="n">
-        <v>7303457</v>
+        <v>7303020</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -18491,10 +18491,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>118640752</v>
+        <v>118640701</v>
       </c>
       <c r="B167" t="n">
-        <v>82263</v>
+        <v>79073</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18507,21 +18507,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1312</v>
+        <v>229821</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>715548</v>
+        <v>715173</v>
       </c>
       <c r="R167" t="n">
-        <v>7303162</v>
+        <v>7303457</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18581,12 +18581,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -19661,10 +19661,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>118639944</v>
+        <v>118628524</v>
       </c>
       <c r="B178" t="n">
-        <v>96807</v>
+        <v>78484</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19673,38 +19673,38 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Slaktarberget, Pi lm</t>
+          <t>Slaktarberget (Slaktarberget), Pi lm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>715553</v>
+        <v>715298</v>
       </c>
       <c r="R178" t="n">
-        <v>7303125</v>
+        <v>7302970</v>
       </c>
       <c r="S178" t="n">
         <v>1</v>
@@ -19734,9 +19734,19 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19751,26 +19761,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
-        </is>
-      </c>
-      <c r="AY178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>118638441</v>
+        <v>118640697</v>
       </c>
       <c r="B179" t="n">
-        <v>78221</v>
+        <v>79102</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19783,21 +19789,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19807,13 +19813,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>715326</v>
+        <v>715320</v>
       </c>
       <c r="R179" t="n">
-        <v>7303317</v>
+        <v>7303018</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19857,12 +19863,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -19873,10 +19879,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>118628524</v>
+        <v>118642120</v>
       </c>
       <c r="B180" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19889,37 +19895,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Slaktarberget (Slaktarberget), Pi lm</t>
+          <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>715298</v>
+        <v>715155</v>
       </c>
       <c r="R180" t="n">
-        <v>7302970</v>
+        <v>7303431</v>
       </c>
       <c r="S180" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19946,46 +19952,41 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AD180" t="b">
         <v>0</v>
       </c>
       <c r="AE180" t="b">
         <v>0</v>
       </c>
+      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY180" t="inlineStr"/>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>118640697</v>
+        <v>118641452</v>
       </c>
       <c r="B181" t="n">
         <v>79102</v>
@@ -20025,13 +20026,13 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>715320</v>
+        <v>715513</v>
       </c>
       <c r="R181" t="n">
-        <v>7303018</v>
+        <v>7302990</v>
       </c>
       <c r="S181" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20075,12 +20076,12 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
@@ -20091,10 +20092,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>118642120</v>
+        <v>118639944</v>
       </c>
       <c r="B182" t="n">
-        <v>78220</v>
+        <v>96807</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20103,25 +20104,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20131,13 +20132,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>715155</v>
+        <v>715553</v>
       </c>
       <c r="R182" t="n">
-        <v>7303431</v>
+        <v>7303125</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20175,19 +20176,18 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -20198,10 +20198,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>118641452</v>
+        <v>118638441</v>
       </c>
       <c r="B183" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20214,21 +20214,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20238,10 +20238,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>715513</v>
+        <v>715326</v>
       </c>
       <c r="R183" t="n">
-        <v>7302990</v>
+        <v>7303317</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20288,12 +20288,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -21053,10 +21053,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>118642117</v>
+        <v>118639955</v>
       </c>
       <c r="B191" t="n">
-        <v>57306</v>
+        <v>90522</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21069,45 +21069,37 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>715634</v>
+        <v>715555</v>
       </c>
       <c r="R191" t="n">
-        <v>7303012</v>
+        <v>7303134</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -21137,11 +21129,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>hack</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21156,12 +21143,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -21172,10 +21159,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>118641458</v>
+        <v>118638460</v>
       </c>
       <c r="B192" t="n">
-        <v>96807</v>
+        <v>77868</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21184,25 +21171,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>221941</v>
+        <v>6437</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21212,10 +21199,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>715161</v>
+        <v>715129</v>
       </c>
       <c r="R192" t="n">
-        <v>7303437</v>
+        <v>7303486</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21262,12 +21249,12 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -21278,10 +21265,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>118639955</v>
+        <v>118639958</v>
       </c>
       <c r="B193" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21294,21 +21281,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21318,10 +21305,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>715555</v>
+        <v>715166</v>
       </c>
       <c r="R193" t="n">
-        <v>7303134</v>
+        <v>7303460</v>
       </c>
       <c r="S193" t="n">
         <v>1</v>
@@ -21384,10 +21371,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>118638460</v>
+        <v>118638453</v>
       </c>
       <c r="B194" t="n">
-        <v>77868</v>
+        <v>78484</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21400,21 +21387,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21424,10 +21411,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>715129</v>
+        <v>715390</v>
       </c>
       <c r="R194" t="n">
-        <v>7303486</v>
+        <v>7302980</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21490,10 +21477,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>118639958</v>
+        <v>118640720</v>
       </c>
       <c r="B195" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21506,21 +21493,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21530,13 +21517,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>715166</v>
+        <v>715120</v>
       </c>
       <c r="R195" t="n">
-        <v>7303460</v>
+        <v>7302906</v>
       </c>
       <c r="S195" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21580,12 +21567,12 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -21596,7 +21583,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>118638453</v>
+        <v>118640759</v>
       </c>
       <c r="B196" t="n">
         <v>78484</v>
@@ -21636,10 +21623,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>715390</v>
+        <v>715489</v>
       </c>
       <c r="R196" t="n">
-        <v>7302980</v>
+        <v>7303003</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21686,12 +21673,12 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
@@ -21702,10 +21689,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>118640720</v>
+        <v>118639262</v>
       </c>
       <c r="B197" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21718,37 +21705,40 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>715120</v>
+        <v>715520</v>
       </c>
       <c r="R197" t="n">
-        <v>7302906</v>
+        <v>7303163</v>
       </c>
       <c r="S197" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21786,18 +21776,19 @@
       <c r="AE197" t="b">
         <v>0</v>
       </c>
+      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -21808,10 +21799,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>118640759</v>
+        <v>118637554</v>
       </c>
       <c r="B198" t="n">
-        <v>78484</v>
+        <v>79593</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21820,25 +21811,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21848,10 +21839,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>715489</v>
+        <v>715103</v>
       </c>
       <c r="R198" t="n">
-        <v>7303003</v>
+        <v>7302976</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21898,12 +21889,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -21914,10 +21905,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>118639262</v>
+        <v>118641458</v>
       </c>
       <c r="B199" t="n">
-        <v>78484</v>
+        <v>96807</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21926,44 +21917,41 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>715520</v>
+        <v>715161</v>
       </c>
       <c r="R199" t="n">
-        <v>7303163</v>
+        <v>7303437</v>
       </c>
       <c r="S199" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -22001,19 +21989,18 @@
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -22024,10 +22011,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>118637554</v>
+        <v>118642117</v>
       </c>
       <c r="B200" t="n">
-        <v>79593</v>
+        <v>57306</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22036,38 +22023,46 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>715103</v>
+        <v>715634</v>
       </c>
       <c r="R200" t="n">
-        <v>7302976</v>
+        <v>7303012</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22102,6 +22097,11 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
       <c r="AD200" t="b">
         <v>0</v>
       </c>
@@ -22114,12 +22114,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">

--- a/artfynd/A 29088-2023 artfynd.xlsx
+++ b/artfynd/A 29088-2023 artfynd.xlsx
@@ -8716,7 +8716,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118638435</v>
+        <v>118640700</v>
       </c>
       <c r="B76" t="n">
         <v>79102</v>
@@ -8756,13 +8756,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715205</v>
+        <v>715069</v>
       </c>
       <c r="R76" t="n">
-        <v>7303041</v>
+        <v>7302903</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8806,22 +8806,26 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118639919</v>
+        <v>118639959</v>
       </c>
       <c r="B77" t="n">
-        <v>104925</v>
+        <v>78484</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8830,25 +8834,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8858,10 +8862,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715338</v>
+        <v>715226</v>
       </c>
       <c r="R77" t="n">
-        <v>7303350</v>
+        <v>7303445</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8924,10 +8928,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118638437</v>
+        <v>118641285</v>
       </c>
       <c r="B78" t="n">
-        <v>97867</v>
+        <v>78220</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8936,38 +8940,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>715347</v>
+        <v>715438</v>
       </c>
       <c r="R78" t="n">
-        <v>7302995</v>
+        <v>7303256</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8997,40 +9004,47 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118640700</v>
+        <v>118638435</v>
       </c>
       <c r="B79" t="n">
         <v>79102</v>
@@ -9070,13 +9084,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>715069</v>
+        <v>715205</v>
       </c>
       <c r="R79" t="n">
-        <v>7302903</v>
+        <v>7303041</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9120,26 +9134,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118639959</v>
+        <v>118638437</v>
       </c>
       <c r="B80" t="n">
-        <v>78484</v>
+        <v>97867</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9148,25 +9158,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9176,13 +9186,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>715226</v>
+        <v>715347</v>
       </c>
       <c r="R80" t="n">
-        <v>7303445</v>
+        <v>7302995</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9226,12 +9236,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9242,10 +9252,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118641285</v>
+        <v>118641293</v>
       </c>
       <c r="B81" t="n">
-        <v>78220</v>
+        <v>78221</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9258,21 +9268,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9575,10 +9585,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118641293</v>
+        <v>118639919</v>
       </c>
       <c r="B84" t="n">
-        <v>78221</v>
+        <v>104925</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9587,44 +9597,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>221725</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715438</v>
+        <v>715338</v>
       </c>
       <c r="R84" t="n">
-        <v>7303256</v>
+        <v>7303350</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9651,43 +9658,36 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10645,10 +10645,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118639939</v>
+        <v>118640750</v>
       </c>
       <c r="B94" t="n">
-        <v>57306</v>
+        <v>90469</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10657,25 +10657,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10685,13 +10685,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715163</v>
+        <v>715571</v>
       </c>
       <c r="R94" t="n">
-        <v>7303461</v>
+        <v>7303146</v>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10721,11 +10721,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10740,12 +10735,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10756,10 +10751,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118639941</v>
+        <v>118639920</v>
       </c>
       <c r="B95" t="n">
-        <v>57306</v>
+        <v>90430</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10772,21 +10767,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>3242</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10796,10 +10791,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>715267</v>
+        <v>715266</v>
       </c>
       <c r="R95" t="n">
-        <v>7302969</v>
+        <v>7303459</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10832,11 +10827,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10867,10 +10857,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118631512</v>
+        <v>118640749</v>
       </c>
       <c r="B96" t="n">
-        <v>97867</v>
+        <v>78566</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10879,41 +10869,41 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221952</v>
+        <v>864</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Slaktarberget (Slaktarberget), Pi lm</t>
+          <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>715519</v>
+        <v>715571</v>
       </c>
       <c r="R96" t="n">
-        <v>7303165</v>
+        <v>7303146</v>
       </c>
       <c r="S96" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10940,19 +10930,9 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>14:15</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10967,22 +10947,26 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118631323</v>
+        <v>118639953</v>
       </c>
       <c r="B97" t="n">
-        <v>97867</v>
+        <v>90654</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10991,38 +10975,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221952</v>
+        <v>1503</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Slaktarberget (Slaktarberget), Pi lm</t>
+          <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715548</v>
+        <v>715480</v>
       </c>
       <c r="R97" t="n">
-        <v>7303158</v>
+        <v>7302982</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -11052,19 +11036,9 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>14:04</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11079,22 +11053,26 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118638442</v>
+        <v>118642121</v>
       </c>
       <c r="B98" t="n">
-        <v>78221</v>
+        <v>90518</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11107,21 +11085,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>1204</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11131,10 +11109,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>715487</v>
+        <v>715581</v>
       </c>
       <c r="R98" t="n">
-        <v>7302960</v>
+        <v>7303107</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11181,12 +11159,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11197,10 +11175,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118640749</v>
+        <v>118639924</v>
       </c>
       <c r="B99" t="n">
-        <v>78566</v>
+        <v>90504</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11213,21 +11191,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11237,13 +11215,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>715571</v>
+        <v>715338</v>
       </c>
       <c r="R99" t="n">
-        <v>7303146</v>
+        <v>7303353</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11287,12 +11265,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11303,10 +11281,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118639953</v>
+        <v>118639939</v>
       </c>
       <c r="B100" t="n">
-        <v>90654</v>
+        <v>57306</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11315,25 +11293,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1503</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11343,10 +11321,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715480</v>
+        <v>715163</v>
       </c>
       <c r="R100" t="n">
-        <v>7302982</v>
+        <v>7303461</v>
       </c>
       <c r="S100" t="n">
         <v>1</v>
@@ -11379,6 +11357,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11409,10 +11392,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118642121</v>
+        <v>118639941</v>
       </c>
       <c r="B101" t="n">
-        <v>90518</v>
+        <v>57306</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11425,21 +11408,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11449,13 +11432,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715581</v>
+        <v>715267</v>
       </c>
       <c r="R101" t="n">
-        <v>7303107</v>
+        <v>7302969</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11485,6 +11468,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11499,12 +11487,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11515,10 +11503,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118639924</v>
+        <v>118631512</v>
       </c>
       <c r="B102" t="n">
-        <v>90504</v>
+        <v>97867</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11527,38 +11515,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Slaktarberget, Pi lm</t>
+          <t>Slaktarberget (Slaktarberget), Pi lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>715338</v>
+        <v>715519</v>
       </c>
       <c r="R102" t="n">
-        <v>7303353</v>
+        <v>7303165</v>
       </c>
       <c r="S102" t="n">
         <v>1</v>
@@ -11588,9 +11576,19 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11605,26 +11603,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118640750</v>
+        <v>118631323</v>
       </c>
       <c r="B103" t="n">
-        <v>90469</v>
+        <v>97867</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11637,37 +11631,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Slaktarberget, Pi lm</t>
+          <t>Slaktarberget (Slaktarberget), Pi lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>715571</v>
+        <v>715548</v>
       </c>
       <c r="R103" t="n">
-        <v>7303146</v>
+        <v>7303158</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11694,9 +11688,19 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11711,26 +11715,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118639920</v>
+        <v>118638442</v>
       </c>
       <c r="B104" t="n">
-        <v>90430</v>
+        <v>78221</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11743,21 +11743,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11767,13 +11767,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>715266</v>
+        <v>715487</v>
       </c>
       <c r="R104" t="n">
-        <v>7303459</v>
+        <v>7302960</v>
       </c>
       <c r="S104" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11817,12 +11817,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11833,10 +11833,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118640850</v>
+        <v>118637571</v>
       </c>
       <c r="B105" t="n">
-        <v>78484</v>
+        <v>41094</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11849,37 +11849,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>215713</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>715385</v>
+        <v>715388</v>
       </c>
       <c r="R105" t="n">
-        <v>7303019</v>
+        <v>7303274</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11920,26 +11917,29 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118639962</v>
+        <v>118640850</v>
       </c>
       <c r="B106" t="n">
         <v>78484</v>
@@ -11973,19 +11973,22 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>715598</v>
+        <v>715385</v>
       </c>
       <c r="R106" t="n">
-        <v>7302991</v>
+        <v>7303019</v>
       </c>
       <c r="S106" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12023,32 +12026,29 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118637571</v>
+        <v>118639962</v>
       </c>
       <c r="B107" t="n">
-        <v>41094</v>
+        <v>78484</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12061,21 +12061,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>215713</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12085,13 +12085,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>715388</v>
+        <v>715598</v>
       </c>
       <c r="R107" t="n">
-        <v>7303274</v>
+        <v>7302991</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12135,12 +12135,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -13450,10 +13450,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118641221</v>
+        <v>118638461</v>
       </c>
       <c r="B120" t="n">
-        <v>96807</v>
+        <v>90469</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13466,38 +13466,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>715502</v>
+        <v>715146</v>
       </c>
       <c r="R120" t="n">
-        <v>7303165</v>
+        <v>7302931</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13527,50 +13523,43 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118642112</v>
+        <v>118638449</v>
       </c>
       <c r="B121" t="n">
-        <v>97867</v>
+        <v>78484</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13579,25 +13568,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13607,10 +13596,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>715577</v>
+        <v>715526</v>
       </c>
       <c r="R121" t="n">
-        <v>7303094</v>
+        <v>7303109</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13645,11 +13634,6 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>30 stänglar</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -13662,12 +13646,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13678,10 +13662,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118641457</v>
+        <v>118640696</v>
       </c>
       <c r="B122" t="n">
-        <v>96801</v>
+        <v>79102</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13690,25 +13674,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13718,13 +13702,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>715342</v>
+        <v>715398</v>
       </c>
       <c r="R122" t="n">
-        <v>7302986</v>
+        <v>7303002</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13768,12 +13752,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13784,10 +13768,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118641460</v>
+        <v>118640722</v>
       </c>
       <c r="B123" t="n">
-        <v>96807</v>
+        <v>78484</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13796,25 +13780,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13824,13 +13808,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>715166</v>
+        <v>715522</v>
       </c>
       <c r="R123" t="n">
-        <v>7302939</v>
+        <v>7303150</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13874,12 +13858,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13890,10 +13874,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118641454</v>
+        <v>118641221</v>
       </c>
       <c r="B124" t="n">
-        <v>79073</v>
+        <v>96807</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13902,38 +13886,42 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>715510</v>
+        <v>715502</v>
       </c>
       <c r="R124" t="n">
-        <v>7302988</v>
+        <v>7303165</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13963,43 +13951,50 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118638461</v>
+        <v>118642112</v>
       </c>
       <c r="B125" t="n">
-        <v>90469</v>
+        <v>97867</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14012,21 +14007,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14036,10 +14031,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>715146</v>
+        <v>715577</v>
       </c>
       <c r="R125" t="n">
-        <v>7302931</v>
+        <v>7303094</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14074,6 +14069,11 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>30 stänglar</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -14086,12 +14086,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -14102,10 +14102,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118638449</v>
+        <v>118641457</v>
       </c>
       <c r="B126" t="n">
-        <v>78484</v>
+        <v>96801</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14114,25 +14114,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14142,10 +14142,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>715526</v>
+        <v>715342</v>
       </c>
       <c r="R126" t="n">
-        <v>7303109</v>
+        <v>7302986</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14192,12 +14192,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -14208,10 +14208,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118640696</v>
+        <v>118641460</v>
       </c>
       <c r="B127" t="n">
-        <v>79102</v>
+        <v>96807</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14220,25 +14220,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14248,13 +14248,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>715398</v>
+        <v>715166</v>
       </c>
       <c r="R127" t="n">
-        <v>7303002</v>
+        <v>7302939</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14298,12 +14298,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -14314,10 +14314,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118640722</v>
+        <v>118641454</v>
       </c>
       <c r="B128" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14330,21 +14330,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14354,13 +14354,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>715522</v>
+        <v>715510</v>
       </c>
       <c r="R128" t="n">
-        <v>7303150</v>
+        <v>7302988</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14404,12 +14404,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">

--- a/artfynd/A 29088-2023 artfynd.xlsx
+++ b/artfynd/A 29088-2023 artfynd.xlsx
@@ -3874,10 +3874,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118640760</v>
+        <v>118639954</v>
       </c>
       <c r="B31" t="n">
-        <v>78220</v>
+        <v>90654</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3886,25 +3886,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3914,13 +3914,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>715315</v>
+        <v>715100</v>
       </c>
       <c r="R31" t="n">
-        <v>7302930</v>
+        <v>7302912</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3964,12 +3964,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3980,10 +3980,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118640759</v>
+        <v>118640736</v>
       </c>
       <c r="B32" t="n">
-        <v>78484</v>
+        <v>79566</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>715489</v>
+        <v>715305</v>
       </c>
       <c r="R32" t="n">
-        <v>7303003</v>
+        <v>7302918</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118640738</v>
+        <v>118640859</v>
       </c>
       <c r="B33" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4102,34 +4102,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715305</v>
+        <v>715466</v>
       </c>
       <c r="R33" t="n">
-        <v>7302918</v>
+        <v>7302998</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4170,32 +4173,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118640696</v>
+        <v>118638453</v>
       </c>
       <c r="B34" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4208,21 +4208,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4232,13 +4232,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715398</v>
+        <v>715390</v>
       </c>
       <c r="R34" t="n">
-        <v>7303002</v>
+        <v>7302980</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4282,12 +4282,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4298,10 +4298,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118637551</v>
+        <v>118640861</v>
       </c>
       <c r="B35" t="n">
-        <v>79593</v>
+        <v>90749</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4310,38 +4310,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6461</v>
+        <v>65</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715528</v>
+        <v>715466</v>
       </c>
       <c r="R35" t="n">
-        <v>7303056</v>
+        <v>7302998</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4382,32 +4385,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118639954</v>
+        <v>118637564</v>
       </c>
       <c r="B36" t="n">
-        <v>90654</v>
+        <v>78566</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4416,25 +4416,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1503</v>
+        <v>864</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4444,13 +4444,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715100</v>
+        <v>715481</v>
       </c>
       <c r="R36" t="n">
-        <v>7302912</v>
+        <v>7302986</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4494,12 +4494,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4510,10 +4510,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118640736</v>
+        <v>118640738</v>
       </c>
       <c r="B37" t="n">
-        <v>79566</v>
+        <v>79565</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118640859</v>
+        <v>118640696</v>
       </c>
       <c r="B38" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4632,40 +4632,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715466</v>
+        <v>715398</v>
       </c>
       <c r="R38" t="n">
-        <v>7302998</v>
+        <v>7303002</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4703,29 +4700,32 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118638453</v>
+        <v>118637551</v>
       </c>
       <c r="B39" t="n">
-        <v>78484</v>
+        <v>79593</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4734,25 +4734,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715390</v>
+        <v>715528</v>
       </c>
       <c r="R39" t="n">
-        <v>7302980</v>
+        <v>7303056</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4812,12 +4812,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4828,10 +4828,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118640861</v>
+        <v>118640760</v>
       </c>
       <c r="B40" t="n">
-        <v>90749</v>
+        <v>78220</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4840,41 +4840,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715466</v>
+        <v>715315</v>
       </c>
       <c r="R40" t="n">
-        <v>7302998</v>
+        <v>7302930</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4915,29 +4912,32 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118637564</v>
+        <v>118640759</v>
       </c>
       <c r="B41" t="n">
-        <v>78566</v>
+        <v>78484</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4950,21 +4950,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715481</v>
+        <v>715489</v>
       </c>
       <c r="R41" t="n">
-        <v>7302986</v>
+        <v>7303003</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5024,12 +5024,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -6666,10 +6666,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118639963</v>
+        <v>118640692</v>
       </c>
       <c r="B57" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6682,21 +6682,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6706,13 +6706,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>715505</v>
+        <v>715153</v>
       </c>
       <c r="R57" t="n">
-        <v>7302998</v>
+        <v>7303440</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6756,12 +6756,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6772,7 +6772,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118638454</v>
+        <v>118639963</v>
       </c>
       <c r="B58" t="n">
         <v>78484</v>
@@ -6812,13 +6812,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715351</v>
+        <v>715505</v>
       </c>
       <c r="R58" t="n">
-        <v>7302999</v>
+        <v>7302998</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6862,12 +6862,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6878,10 +6878,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118642117</v>
+        <v>118638454</v>
       </c>
       <c r="B59" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6894,42 +6894,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>715634</v>
+        <v>715351</v>
       </c>
       <c r="R59" t="n">
-        <v>7303012</v>
+        <v>7302999</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6964,11 +6956,6 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6981,12 +6968,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6997,7 +6984,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118640755</v>
+        <v>118642117</v>
       </c>
       <c r="B60" t="n">
         <v>57306</v>
@@ -7031,16 +7018,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715615</v>
+        <v>715634</v>
       </c>
       <c r="R60" t="n">
-        <v>7303127</v>
+        <v>7303012</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7077,7 +7072,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7092,12 +7087,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7108,10 +7103,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118640692</v>
+        <v>118640755</v>
       </c>
       <c r="B61" t="n">
-        <v>79102</v>
+        <v>57306</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7124,21 +7119,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7148,13 +7143,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715153</v>
+        <v>715615</v>
       </c>
       <c r="R61" t="n">
-        <v>7303440</v>
+        <v>7303127</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7184,6 +7179,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7198,12 +7198,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7431,10 +7431,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118637571</v>
+        <v>118640713</v>
       </c>
       <c r="B64" t="n">
-        <v>41094</v>
+        <v>78221</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7447,21 +7447,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>215713</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7471,13 +7471,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715388</v>
+        <v>715322</v>
       </c>
       <c r="R64" t="n">
-        <v>7303274</v>
+        <v>7303020</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7521,12 +7521,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7537,7 +7537,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118640713</v>
+        <v>118639947</v>
       </c>
       <c r="B65" t="n">
         <v>78221</v>
@@ -7577,13 +7577,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715322</v>
+        <v>715413</v>
       </c>
       <c r="R65" t="n">
-        <v>7303020</v>
+        <v>7302983</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7627,12 +7627,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118639947</v>
+        <v>118637571</v>
       </c>
       <c r="B66" t="n">
-        <v>78221</v>
+        <v>41094</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7659,21 +7659,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>215713</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7683,13 +7683,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715413</v>
+        <v>715388</v>
       </c>
       <c r="R66" t="n">
-        <v>7302983</v>
+        <v>7303274</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7733,12 +7733,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -8502,10 +8502,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118640742</v>
+        <v>118640700</v>
       </c>
       <c r="B74" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8518,21 +8518,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8542,13 +8542,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>715196</v>
+        <v>715069</v>
       </c>
       <c r="R74" t="n">
-        <v>7302941</v>
+        <v>7302903</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8592,12 +8592,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8608,10 +8608,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118638447</v>
+        <v>118637575</v>
       </c>
       <c r="B75" t="n">
-        <v>78566</v>
+        <v>78484</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8624,21 +8624,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8648,10 +8648,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715583</v>
+        <v>715517</v>
       </c>
       <c r="R75" t="n">
-        <v>7303046</v>
+        <v>7303148</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8698,12 +8698,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8714,10 +8714,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118639922</v>
+        <v>118640742</v>
       </c>
       <c r="B76" t="n">
-        <v>95394</v>
+        <v>78484</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8730,21 +8730,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8754,13 +8754,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715303</v>
+        <v>715196</v>
       </c>
       <c r="R76" t="n">
-        <v>7302995</v>
+        <v>7302941</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8804,12 +8804,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8820,10 +8820,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118640691</v>
+        <v>118638447</v>
       </c>
       <c r="B77" t="n">
-        <v>95394</v>
+        <v>78566</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8836,21 +8836,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>864</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8860,13 +8860,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715323</v>
+        <v>715583</v>
       </c>
       <c r="R77" t="n">
-        <v>7303053</v>
+        <v>7303046</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8910,12 +8910,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8926,10 +8926,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118640943</v>
+        <v>118639922</v>
       </c>
       <c r="B78" t="n">
-        <v>78484</v>
+        <v>95394</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8942,40 +8942,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>715563</v>
+        <v>715303</v>
       </c>
       <c r="R78" t="n">
-        <v>7303066</v>
+        <v>7302995</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9013,29 +9010,32 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118640700</v>
+        <v>118640691</v>
       </c>
       <c r="B79" t="n">
-        <v>79102</v>
+        <v>95394</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9048,21 +9048,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9072,10 +9072,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>715069</v>
+        <v>715323</v>
       </c>
       <c r="R79" t="n">
-        <v>7302903</v>
+        <v>7303053</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -9138,7 +9138,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118637575</v>
+        <v>118640943</v>
       </c>
       <c r="B80" t="n">
         <v>78484</v>
@@ -9172,16 +9172,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>715517</v>
+        <v>715563</v>
       </c>
       <c r="R80" t="n">
-        <v>7303148</v>
+        <v>7303066</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9222,25 +9225,22 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -12014,10 +12014,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118642115</v>
+        <v>118640694</v>
       </c>
       <c r="B107" t="n">
-        <v>97867</v>
+        <v>79102</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12026,25 +12026,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12054,13 +12054,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>715580</v>
+        <v>715510</v>
       </c>
       <c r="R107" t="n">
-        <v>7303094</v>
+        <v>7302980</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12090,11 +12090,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>19 stänglar</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12109,12 +12104,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -12125,10 +12120,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118640704</v>
+        <v>118640735</v>
       </c>
       <c r="B108" t="n">
-        <v>79073</v>
+        <v>79594</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12137,25 +12132,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12165,13 +12160,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>715432</v>
+        <v>715318</v>
       </c>
       <c r="R108" t="n">
-        <v>7302962</v>
+        <v>7302900</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12215,12 +12210,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12231,10 +12226,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118640712</v>
+        <v>118642115</v>
       </c>
       <c r="B109" t="n">
-        <v>78221</v>
+        <v>97867</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12243,25 +12238,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12271,13 +12266,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>715327</v>
+        <v>715580</v>
       </c>
       <c r="R109" t="n">
-        <v>7303326</v>
+        <v>7303094</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12307,6 +12302,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>19 stänglar</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12321,12 +12321,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12337,10 +12337,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118642122</v>
+        <v>118640704</v>
       </c>
       <c r="B110" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12353,21 +12353,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12377,13 +12377,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>715610</v>
+        <v>715432</v>
       </c>
       <c r="R110" t="n">
-        <v>7303020</v>
+        <v>7302962</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12427,12 +12427,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12443,10 +12443,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118641146</v>
+        <v>118640712</v>
       </c>
       <c r="B111" t="n">
-        <v>90654</v>
+        <v>78221</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12455,44 +12455,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>715253</v>
+        <v>715327</v>
       </c>
       <c r="R111" t="n">
-        <v>7302997</v>
+        <v>7303326</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12519,50 +12516,43 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr"/>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118639952</v>
+        <v>118642122</v>
       </c>
       <c r="B112" t="n">
-        <v>90518</v>
+        <v>78484</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12575,21 +12565,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12599,13 +12589,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>715088</v>
+        <v>715610</v>
       </c>
       <c r="R112" t="n">
-        <v>7302934</v>
+        <v>7303020</v>
       </c>
       <c r="S112" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12649,12 +12639,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12665,10 +12655,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118640694</v>
+        <v>118641146</v>
       </c>
       <c r="B113" t="n">
-        <v>79102</v>
+        <v>90654</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12677,41 +12667,44 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>715510</v>
+        <v>715253</v>
       </c>
       <c r="R113" t="n">
-        <v>7302980</v>
+        <v>7302997</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12738,43 +12731,50 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118640735</v>
+        <v>118639952</v>
       </c>
       <c r="B114" t="n">
-        <v>79594</v>
+        <v>90518</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12783,25 +12783,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12811,13 +12811,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>715318</v>
+        <v>715088</v>
       </c>
       <c r="R114" t="n">
-        <v>7302900</v>
+        <v>7302934</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12861,12 +12861,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -15563,10 +15563,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118637541</v>
+        <v>118640748</v>
       </c>
       <c r="B140" t="n">
-        <v>91791</v>
+        <v>79102</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15575,25 +15575,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15603,10 +15603,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>715154</v>
+        <v>715313</v>
       </c>
       <c r="R140" t="n">
-        <v>7303454</v>
+        <v>7302940</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15653,12 +15653,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15669,10 +15669,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118639920</v>
+        <v>118640720</v>
       </c>
       <c r="B141" t="n">
-        <v>90430</v>
+        <v>78220</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15685,21 +15685,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15709,13 +15709,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>715266</v>
+        <v>715120</v>
       </c>
       <c r="R141" t="n">
-        <v>7303459</v>
+        <v>7302906</v>
       </c>
       <c r="S141" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15759,12 +15759,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15775,10 +15775,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118639962</v>
+        <v>118637541</v>
       </c>
       <c r="B142" t="n">
-        <v>78484</v>
+        <v>91791</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15787,25 +15787,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15815,13 +15815,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>715598</v>
+        <v>715154</v>
       </c>
       <c r="R142" t="n">
-        <v>7302991</v>
+        <v>7303454</v>
       </c>
       <c r="S142" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15865,12 +15865,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15881,10 +15881,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118638449</v>
+        <v>118639920</v>
       </c>
       <c r="B143" t="n">
-        <v>78484</v>
+        <v>90430</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15897,21 +15897,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15921,13 +15921,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>715526</v>
+        <v>715266</v>
       </c>
       <c r="R143" t="n">
-        <v>7303109</v>
+        <v>7303459</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15971,12 +15971,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -15987,10 +15987,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118640729</v>
+        <v>118638446</v>
       </c>
       <c r="B144" t="n">
-        <v>77868</v>
+        <v>78566</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16003,21 +16003,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6437</v>
+        <v>864</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16027,13 +16027,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>715120</v>
+        <v>715544</v>
       </c>
       <c r="R144" t="n">
-        <v>7302906</v>
+        <v>7303077</v>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16077,12 +16077,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -16093,10 +16093,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118642116</v>
+        <v>118637584</v>
       </c>
       <c r="B145" t="n">
-        <v>57306</v>
+        <v>90749</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16105,46 +16105,38 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>65</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>715240</v>
+        <v>715318</v>
       </c>
       <c r="R145" t="n">
-        <v>7303369</v>
+        <v>7303032</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16179,11 +16171,6 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -16196,12 +16183,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -16212,10 +16199,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118638446</v>
+        <v>118641087</v>
       </c>
       <c r="B146" t="n">
-        <v>78566</v>
+        <v>57401</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16224,38 +16211,46 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>864</v>
+        <v>103031</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>715544</v>
+        <v>715124</v>
       </c>
       <c r="R146" t="n">
-        <v>7303077</v>
+        <v>7302962</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16285,9 +16280,19 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16302,26 +16307,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118637584</v>
+        <v>118639962</v>
       </c>
       <c r="B147" t="n">
-        <v>90749</v>
+        <v>78484</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16330,25 +16331,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16358,13 +16359,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>715318</v>
+        <v>715598</v>
       </c>
       <c r="R147" t="n">
-        <v>7303032</v>
+        <v>7302991</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16408,12 +16409,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -16424,10 +16425,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118641463</v>
+        <v>118638449</v>
       </c>
       <c r="B148" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16436,25 +16437,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16464,10 +16465,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>715474</v>
+        <v>715526</v>
       </c>
       <c r="R148" t="n">
-        <v>7303165</v>
+        <v>7303109</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16514,12 +16515,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -16530,10 +16531,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118641087</v>
+        <v>118640729</v>
       </c>
       <c r="B149" t="n">
-        <v>57401</v>
+        <v>77868</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16542,49 +16543,41 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103031</v>
+        <v>6437</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>715124</v>
+        <v>715120</v>
       </c>
       <c r="R149" t="n">
-        <v>7302962</v>
+        <v>7302906</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16611,19 +16604,9 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16638,22 +16621,26 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr"/>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118630550</v>
+        <v>118642116</v>
       </c>
       <c r="B150" t="n">
-        <v>97867</v>
+        <v>57306</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16662,45 +16649,49 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Slaktarberget (Slaktarberget), Pi lm</t>
+          <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>715587</v>
+        <v>715240</v>
       </c>
       <c r="R150" t="n">
-        <v>7303046</v>
+        <v>7303369</v>
       </c>
       <c r="S150" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16727,19 +16718,14 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16754,22 +16740,26 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY150" t="inlineStr"/>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118640748</v>
+        <v>118641463</v>
       </c>
       <c r="B151" t="n">
-        <v>79102</v>
+        <v>79601</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16778,25 +16768,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16806,10 +16796,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>715313</v>
+        <v>715474</v>
       </c>
       <c r="R151" t="n">
-        <v>7302940</v>
+        <v>7303165</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16856,12 +16846,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -16872,10 +16862,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118640720</v>
+        <v>118640757</v>
       </c>
       <c r="B152" t="n">
-        <v>78220</v>
+        <v>56502</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16884,41 +16874,49 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>715120</v>
+        <v>715605</v>
       </c>
       <c r="R152" t="n">
-        <v>7302906</v>
+        <v>7303120</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16962,12 +16960,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -16978,10 +16976,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118640757</v>
+        <v>118637537</v>
       </c>
       <c r="B153" t="n">
-        <v>56502</v>
+        <v>97867</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16994,42 +16992,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>715605</v>
+        <v>715401</v>
       </c>
       <c r="R153" t="n">
-        <v>7303120</v>
+        <v>7303030</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17076,12 +17066,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -17092,10 +17082,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118637537</v>
+        <v>118637547</v>
       </c>
       <c r="B154" t="n">
-        <v>97867</v>
+        <v>96807</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17108,21 +17098,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17132,10 +17122,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>715401</v>
+        <v>715129</v>
       </c>
       <c r="R154" t="n">
-        <v>7303030</v>
+        <v>7303443</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17198,10 +17188,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118637547</v>
+        <v>118630550</v>
       </c>
       <c r="B155" t="n">
-        <v>96807</v>
+        <v>97867</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17214,37 +17204,41 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221941</v>
+        <v>221952</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Slaktarberget, Pi lm</t>
+          <t>Slaktarberget (Slaktarberget), Pi lm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>715129</v>
+        <v>715587</v>
       </c>
       <c r="R155" t="n">
-        <v>7303443</v>
+        <v>7303046</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17271,9 +17265,19 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17288,19 +17292,15 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -23715,10 +23715,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>118639970</v>
+        <v>118638443</v>
       </c>
       <c r="B216" t="n">
-        <v>91779</v>
+        <v>91795</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -23727,25 +23727,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -23755,13 +23755,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>715124</v>
+        <v>715116</v>
       </c>
       <c r="R216" t="n">
-        <v>7302952</v>
+        <v>7302967</v>
       </c>
       <c r="S216" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -23805,12 +23805,12 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
@@ -23821,10 +23821,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>118640923</v>
+        <v>118637556</v>
       </c>
       <c r="B217" t="n">
-        <v>78484</v>
+        <v>91969</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -23837,37 +23837,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>715549</v>
+        <v>715262</v>
       </c>
       <c r="R217" t="n">
-        <v>7303075</v>
+        <v>7302967</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23908,29 +23905,32 @@
       <c r="AE217" t="b">
         <v>0</v>
       </c>
-      <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY217" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>118640786</v>
+        <v>118639970</v>
       </c>
       <c r="B218" t="n">
-        <v>78484</v>
+        <v>91779</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -23939,44 +23939,41 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>715278</v>
+        <v>715124</v>
       </c>
       <c r="R218" t="n">
-        <v>7302945</v>
+        <v>7302952</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -24014,29 +24011,32 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
-      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY218" t="inlineStr"/>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>118638443</v>
+        <v>118641407</v>
       </c>
       <c r="B219" t="n">
-        <v>91795</v>
+        <v>56494</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24049,24 +24049,32 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>2059</v>
+        <v>102612</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
@@ -24076,7 +24084,7 @@
         <v>715116</v>
       </c>
       <c r="R219" t="n">
-        <v>7302967</v>
+        <v>7303477</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24106,9 +24114,19 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24123,26 +24141,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>118637556</v>
+        <v>118640923</v>
       </c>
       <c r="B220" t="n">
-        <v>91969</v>
+        <v>78484</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24155,34 +24169,37 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>715262</v>
+        <v>715549</v>
       </c>
       <c r="R220" t="n">
-        <v>7302967</v>
+        <v>7303075</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24223,29 +24240,26 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
+      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>118638452</v>
+        <v>118640786</v>
       </c>
       <c r="B221" t="n">
         <v>78484</v>
@@ -24279,16 +24293,19 @@
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>715474</v>
+        <v>715278</v>
       </c>
       <c r="R221" t="n">
-        <v>7302970</v>
+        <v>7302945</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24329,29 +24346,26 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
+      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>118639960</v>
+        <v>118638452</v>
       </c>
       <c r="B222" t="n">
         <v>78484</v>
@@ -24391,13 +24405,13 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>715598</v>
+        <v>715474</v>
       </c>
       <c r="R222" t="n">
-        <v>7303047</v>
+        <v>7302970</v>
       </c>
       <c r="S222" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -24441,12 +24455,12 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
@@ -24457,10 +24471,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>118639938</v>
+        <v>118639960</v>
       </c>
       <c r="B223" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -24473,21 +24487,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -24497,10 +24511,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>715254</v>
+        <v>715598</v>
       </c>
       <c r="R223" t="n">
-        <v>7302973</v>
+        <v>7303047</v>
       </c>
       <c r="S223" t="n">
         <v>1</v>
@@ -24533,11 +24547,6 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>Gammalt hack</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24568,10 +24577,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>118640724</v>
+        <v>118639938</v>
       </c>
       <c r="B224" t="n">
-        <v>78129</v>
+        <v>57306</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -24584,21 +24593,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -24608,13 +24617,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>715482</v>
+        <v>715254</v>
       </c>
       <c r="R224" t="n">
-        <v>7302975</v>
+        <v>7302973</v>
       </c>
       <c r="S224" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -24644,6 +24653,11 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Gammalt hack</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24658,12 +24672,12 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -24674,10 +24688,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>118641407</v>
+        <v>118640724</v>
       </c>
       <c r="B225" t="n">
-        <v>56494</v>
+        <v>78129</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24690,45 +24704,37 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>102612</v>
+        <v>353</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>715116</v>
+        <v>715482</v>
       </c>
       <c r="R225" t="n">
-        <v>7303477</v>
+        <v>7302975</v>
       </c>
       <c r="S225" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -24755,19 +24761,9 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24782,15 +24778,19 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY225" t="inlineStr"/>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25021,10 +25021,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>118639969</v>
+        <v>118640695</v>
       </c>
       <c r="B228" t="n">
-        <v>90749</v>
+        <v>79102</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -25033,25 +25033,25 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -25061,13 +25061,13 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>715425</v>
+        <v>715434</v>
       </c>
       <c r="R228" t="n">
-        <v>7302976</v>
+        <v>7302966</v>
       </c>
       <c r="S228" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -25111,12 +25111,12 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
@@ -25127,10 +25127,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>118638442</v>
+        <v>118639927</v>
       </c>
       <c r="B229" t="n">
-        <v>78221</v>
+        <v>57443</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -25143,21 +25143,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -25167,13 +25167,13 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>715487</v>
+        <v>715468</v>
       </c>
       <c r="R229" t="n">
-        <v>7302960</v>
+        <v>7302980</v>
       </c>
       <c r="S229" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -25203,6 +25203,11 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>3-4 stycken</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25217,12 +25222,12 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
@@ -25233,10 +25238,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>118640695</v>
+        <v>118638442</v>
       </c>
       <c r="B230" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -25249,21 +25254,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -25273,13 +25278,13 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>715434</v>
+        <v>715487</v>
       </c>
       <c r="R230" t="n">
-        <v>7302966</v>
+        <v>7302960</v>
       </c>
       <c r="S230" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -25323,12 +25328,12 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
@@ -25869,10 +25874,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>118639927</v>
+        <v>118639969</v>
       </c>
       <c r="B236" t="n">
-        <v>57443</v>
+        <v>90749</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25881,25 +25886,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>103021</v>
+        <v>65</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -25909,10 +25914,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>715468</v>
+        <v>715425</v>
       </c>
       <c r="R236" t="n">
-        <v>7302980</v>
+        <v>7302976</v>
       </c>
       <c r="S236" t="n">
         <v>1</v>
@@ -25945,11 +25950,6 @@
       <c r="AA236" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>3-4 stycken</t>
         </is>
       </c>
       <c r="AD236" t="b">

--- a/artfynd/A 29088-2023 artfynd.xlsx
+++ b/artfynd/A 29088-2023 artfynd.xlsx
@@ -2692,10 +2692,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118640618</v>
+        <v>118640638</v>
       </c>
       <c r="B20" t="n">
-        <v>96814</v>
+        <v>91976</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2704,41 +2704,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715063</v>
+        <v>715067</v>
       </c>
       <c r="R20" t="n">
-        <v>7302905</v>
+        <v>7302903</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2776,28 +2779,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118637557</v>
+        <v>118640850</v>
       </c>
       <c r="B21" t="n">
-        <v>78228</v>
+        <v>78491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2810,34 +2814,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715433</v>
+        <v>715385</v>
       </c>
       <c r="R21" t="n">
-        <v>7303247</v>
+        <v>7303019</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2885,26 +2892,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118641187</v>
+        <v>118640859</v>
       </c>
       <c r="B22" t="n">
-        <v>57443</v>
+        <v>78491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2917,35 +2920,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2953,10 +2947,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715514</v>
+        <v>715466</v>
       </c>
       <c r="R22" t="n">
-        <v>7303116</v>
+        <v>7302998</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2986,27 +2980,18 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3025,10 +3010,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118640638</v>
+        <v>118640730</v>
       </c>
       <c r="B23" t="n">
-        <v>91976</v>
+        <v>77875</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3041,40 +3026,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715067</v>
+        <v>715096</v>
       </c>
       <c r="R23" t="n">
-        <v>7302903</v>
+        <v>7302918</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3112,26 +3094,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118640850</v>
+        <v>118640744</v>
       </c>
       <c r="B24" t="n">
         <v>78491</v>
@@ -3165,19 +3150,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>715385</v>
+        <v>715172</v>
       </c>
       <c r="R24" t="n">
-        <v>7303019</v>
+        <v>7303561</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3218,26 +3200,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Richard Johansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118640859</v>
+        <v>118640786</v>
       </c>
       <c r="B25" t="n">
         <v>78491</v>
@@ -3280,10 +3265,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715466</v>
+        <v>715278</v>
       </c>
       <c r="R25" t="n">
-        <v>7302998</v>
+        <v>7302945</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3343,10 +3328,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118640730</v>
+        <v>118639963</v>
       </c>
       <c r="B26" t="n">
-        <v>77875</v>
+        <v>78491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3359,21 +3344,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3383,13 +3368,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>715096</v>
+        <v>715505</v>
       </c>
       <c r="R26" t="n">
-        <v>7302918</v>
+        <v>7302998</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3433,12 +3418,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3449,7 +3434,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118640744</v>
+        <v>118640759</v>
       </c>
       <c r="B27" t="n">
         <v>78491</v>
@@ -3489,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715172</v>
+        <v>715489</v>
       </c>
       <c r="R27" t="n">
-        <v>7303561</v>
+        <v>7303003</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3555,10 +3540,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118640786</v>
+        <v>118637565</v>
       </c>
       <c r="B28" t="n">
-        <v>78491</v>
+        <v>91123</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3571,37 +3556,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5454</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715278</v>
+        <v>715247</v>
       </c>
       <c r="R28" t="n">
-        <v>7302945</v>
+        <v>7302980</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3642,29 +3624,32 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118639963</v>
+        <v>118637563</v>
       </c>
       <c r="B29" t="n">
-        <v>78491</v>
+        <v>78227</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3677,21 +3662,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3701,13 +3686,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715505</v>
+        <v>715432</v>
       </c>
       <c r="R29" t="n">
-        <v>7302998</v>
+        <v>7303244</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3751,12 +3736,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3767,10 +3752,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118640759</v>
+        <v>118639942</v>
       </c>
       <c r="B30" t="n">
-        <v>78491</v>
+        <v>57306</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3783,21 +3768,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3807,13 +3792,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>715489</v>
+        <v>715591</v>
       </c>
       <c r="R30" t="n">
-        <v>7303003</v>
+        <v>7303053</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3857,12 +3842,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3873,10 +3858,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118637565</v>
+        <v>118641187</v>
       </c>
       <c r="B31" t="n">
-        <v>91123</v>
+        <v>57443</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3889,34 +3874,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5454</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>715247</v>
+        <v>715514</v>
       </c>
       <c r="R31" t="n">
-        <v>7302980</v>
+        <v>7303116</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3946,9 +3943,19 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,26 +3970,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118637563</v>
+        <v>118640618</v>
       </c>
       <c r="B32" t="n">
-        <v>78227</v>
+        <v>96814</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3991,25 +3994,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4019,13 +4022,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>715432</v>
+        <v>715063</v>
       </c>
       <c r="R32" t="n">
-        <v>7303244</v>
+        <v>7302905</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4069,26 +4072,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118639942</v>
+        <v>118637557</v>
       </c>
       <c r="B33" t="n">
-        <v>57306</v>
+        <v>78228</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4101,21 +4100,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4125,13 +4124,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715591</v>
+        <v>715433</v>
       </c>
       <c r="R33" t="n">
-        <v>7303053</v>
+        <v>7303247</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4169,18 +4168,19 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -5579,10 +5579,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118637583</v>
+        <v>118640757</v>
       </c>
       <c r="B47" t="n">
-        <v>90756</v>
+        <v>56502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5591,38 +5591,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715318</v>
+        <v>715605</v>
       </c>
       <c r="R47" t="n">
-        <v>7303030</v>
+        <v>7303120</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5669,12 +5677,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5685,10 +5693,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118639922</v>
+        <v>118637583</v>
       </c>
       <c r="B48" t="n">
-        <v>95401</v>
+        <v>90756</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5697,25 +5705,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5725,13 +5733,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>715303</v>
+        <v>715318</v>
       </c>
       <c r="R48" t="n">
-        <v>7302995</v>
+        <v>7303030</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5775,12 +5783,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5791,10 +5799,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118640751</v>
+        <v>118639922</v>
       </c>
       <c r="B49" t="n">
-        <v>78573</v>
+        <v>95401</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5807,21 +5815,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5831,13 +5839,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>715568</v>
+        <v>715303</v>
       </c>
       <c r="R49" t="n">
-        <v>7303147</v>
+        <v>7302995</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5881,12 +5889,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5897,10 +5905,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118637552</v>
+        <v>118640751</v>
       </c>
       <c r="B50" t="n">
-        <v>79600</v>
+        <v>78573</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5909,25 +5917,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5937,10 +5945,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>715224</v>
+        <v>715568</v>
       </c>
       <c r="R50" t="n">
-        <v>7303009</v>
+        <v>7303147</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5987,12 +5995,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6321,10 +6329,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118640757</v>
+        <v>118637552</v>
       </c>
       <c r="B54" t="n">
-        <v>56502</v>
+        <v>79600</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6337,42 +6345,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715605</v>
+        <v>715224</v>
       </c>
       <c r="R54" t="n">
-        <v>7303120</v>
+        <v>7303009</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6419,12 +6419,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6866,10 +6866,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118638459</v>
+        <v>118641457</v>
       </c>
       <c r="B59" t="n">
-        <v>77423</v>
+        <v>96808</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6878,25 +6878,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6487</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>715121</v>
+        <v>715342</v>
       </c>
       <c r="R59" t="n">
-        <v>7303483</v>
+        <v>7302986</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6950,19 +6950,18 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6973,10 +6972,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118639923</v>
+        <v>118640713</v>
       </c>
       <c r="B60" t="n">
-        <v>90476</v>
+        <v>78228</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6985,25 +6984,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7013,13 +7012,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715474</v>
+        <v>715322</v>
       </c>
       <c r="R60" t="n">
-        <v>7303165</v>
+        <v>7303020</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7063,12 +7062,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7079,10 +7078,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118641457</v>
+        <v>118639947</v>
       </c>
       <c r="B61" t="n">
-        <v>96808</v>
+        <v>78228</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7091,25 +7090,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7119,13 +7118,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715342</v>
+        <v>715413</v>
       </c>
       <c r="R61" t="n">
-        <v>7302986</v>
+        <v>7302983</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7169,12 +7168,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7185,10 +7184,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118640713</v>
+        <v>118628524</v>
       </c>
       <c r="B62" t="n">
-        <v>78228</v>
+        <v>78491</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7201,37 +7200,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Slaktarberget, Pi lm</t>
+          <t>Slaktarberget (Slaktarberget), Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715322</v>
+        <v>715298</v>
       </c>
       <c r="R62" t="n">
-        <v>7303020</v>
+        <v>7302970</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7258,9 +7257,19 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7275,26 +7284,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118639947</v>
+        <v>118637581</v>
       </c>
       <c r="B63" t="n">
-        <v>78228</v>
+        <v>78491</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7307,21 +7312,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7331,13 +7336,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715413</v>
+        <v>715213</v>
       </c>
       <c r="R63" t="n">
-        <v>7302983</v>
+        <v>7302985</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7381,12 +7386,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7397,10 +7402,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118639927</v>
+        <v>118640729</v>
       </c>
       <c r="B64" t="n">
-        <v>57443</v>
+        <v>77875</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7413,21 +7418,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7437,13 +7442,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715468</v>
+        <v>715120</v>
       </c>
       <c r="R64" t="n">
-        <v>7302980</v>
+        <v>7302906</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7473,11 +7478,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>3-4 stycken</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7492,12 +7492,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7508,10 +7508,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118628524</v>
+        <v>118639923</v>
       </c>
       <c r="B65" t="n">
-        <v>78491</v>
+        <v>90476</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7520,38 +7520,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Slaktarberget (Slaktarberget), Pi lm</t>
+          <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715298</v>
+        <v>715474</v>
       </c>
       <c r="R65" t="n">
-        <v>7302970</v>
+        <v>7303165</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7581,19 +7581,9 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7608,22 +7598,26 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118637581</v>
+        <v>118638459</v>
       </c>
       <c r="B66" t="n">
-        <v>78491</v>
+        <v>77423</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7636,21 +7630,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7660,10 +7654,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715213</v>
+        <v>715121</v>
       </c>
       <c r="R66" t="n">
-        <v>7302985</v>
+        <v>7303483</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7704,18 +7698,19 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7726,10 +7721,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118640729</v>
+        <v>118639927</v>
       </c>
       <c r="B67" t="n">
-        <v>77875</v>
+        <v>57443</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7742,21 +7737,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7766,13 +7761,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715120</v>
+        <v>715468</v>
       </c>
       <c r="R67" t="n">
-        <v>7302906</v>
+        <v>7302980</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7802,6 +7797,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>3-4 stycken</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7816,12 +7816,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8786,10 +8786,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118637547</v>
+        <v>118637572</v>
       </c>
       <c r="B77" t="n">
-        <v>96814</v>
+        <v>90529</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8798,25 +8798,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8826,10 +8826,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715129</v>
+        <v>715538</v>
       </c>
       <c r="R77" t="n">
-        <v>7303443</v>
+        <v>7303121</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8892,10 +8892,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118630550</v>
+        <v>118642116</v>
       </c>
       <c r="B78" t="n">
-        <v>97874</v>
+        <v>57306</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8904,45 +8904,49 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Slaktarberget (Slaktarberget), Pi lm</t>
+          <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>715587</v>
+        <v>715240</v>
       </c>
       <c r="R78" t="n">
-        <v>7303046</v>
+        <v>7303369</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8969,19 +8973,14 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8996,22 +8995,26 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118639954</v>
+        <v>118640719</v>
       </c>
       <c r="B79" t="n">
-        <v>90661</v>
+        <v>78227</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9020,25 +9023,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9048,13 +9051,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>715100</v>
+        <v>715171</v>
       </c>
       <c r="R79" t="n">
-        <v>7302912</v>
+        <v>7303435</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9098,12 +9101,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9114,10 +9117,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118640680</v>
+        <v>118639954</v>
       </c>
       <c r="B80" t="n">
-        <v>78491</v>
+        <v>90661</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9126,44 +9129,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>715171</v>
+        <v>715100</v>
       </c>
       <c r="R80" t="n">
-        <v>7302975</v>
+        <v>7302912</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9201,29 +9201,32 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118637572</v>
+        <v>118639921</v>
       </c>
       <c r="B81" t="n">
-        <v>90529</v>
+        <v>90437</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9236,21 +9239,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>3242</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9260,13 +9263,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715538</v>
+        <v>715119</v>
       </c>
       <c r="R81" t="n">
-        <v>7303121</v>
+        <v>7302948</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9310,12 +9313,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9326,10 +9329,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118642116</v>
+        <v>118637551</v>
       </c>
       <c r="B82" t="n">
-        <v>57306</v>
+        <v>79600</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9338,46 +9341,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>715240</v>
+        <v>715528</v>
       </c>
       <c r="R82" t="n">
-        <v>7303369</v>
+        <v>7303056</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9412,11 +9407,6 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9429,12 +9419,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9445,10 +9435,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118640719</v>
+        <v>118640680</v>
       </c>
       <c r="B83" t="n">
-        <v>78227</v>
+        <v>78491</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9461,24 +9451,27 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
@@ -9488,10 +9481,10 @@
         <v>715171</v>
       </c>
       <c r="R83" t="n">
-        <v>7303435</v>
+        <v>7302975</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9529,32 +9522,29 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118638445</v>
+        <v>118640714</v>
       </c>
       <c r="B84" t="n">
-        <v>97853</v>
+        <v>78228</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9563,25 +9553,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9591,13 +9581,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715352</v>
+        <v>715120</v>
       </c>
       <c r="R84" t="n">
-        <v>7302993</v>
+        <v>7302906</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9641,12 +9631,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9657,10 +9647,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118640714</v>
+        <v>118638445</v>
       </c>
       <c r="B85" t="n">
-        <v>78228</v>
+        <v>97853</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9669,25 +9659,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9697,13 +9687,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715120</v>
+        <v>715352</v>
       </c>
       <c r="R85" t="n">
-        <v>7302906</v>
+        <v>7302993</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9747,12 +9737,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9763,10 +9753,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118639921</v>
+        <v>118637547</v>
       </c>
       <c r="B86" t="n">
-        <v>90437</v>
+        <v>96814</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9775,25 +9765,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3242</v>
+        <v>221941</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9803,13 +9793,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715119</v>
+        <v>715129</v>
       </c>
       <c r="R86" t="n">
-        <v>7302948</v>
+        <v>7303443</v>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9853,12 +9843,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9869,10 +9859,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118637551</v>
+        <v>118630550</v>
       </c>
       <c r="B87" t="n">
-        <v>79600</v>
+        <v>97874</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9885,37 +9875,41 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Slaktarberget, Pi lm</t>
+          <t>Slaktarberget (Slaktarberget), Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715528</v>
+        <v>715587</v>
       </c>
       <c r="R87" t="n">
-        <v>7303056</v>
+        <v>7303046</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9942,9 +9936,19 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9959,19 +9963,15 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12877,10 +12877,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118638453</v>
+        <v>118641450</v>
       </c>
       <c r="B115" t="n">
-        <v>78491</v>
+        <v>90476</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12889,25 +12889,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12917,10 +12917,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>715390</v>
+        <v>715402</v>
       </c>
       <c r="R115" t="n">
-        <v>7302980</v>
+        <v>7302984</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12967,12 +12967,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12983,10 +12983,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118639962</v>
+        <v>118638434</v>
       </c>
       <c r="B116" t="n">
-        <v>78491</v>
+        <v>90476</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12995,25 +12995,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>715598</v>
+        <v>715541</v>
       </c>
       <c r="R116" t="n">
-        <v>7302991</v>
+        <v>7303144</v>
       </c>
       <c r="S116" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13073,26 +13073,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118640708</v>
+        <v>118642115</v>
       </c>
       <c r="B117" t="n">
-        <v>78517</v>
+        <v>97874</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13105,21 +13101,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6434</v>
+        <v>221952</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13129,13 +13125,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>715178</v>
+        <v>715580</v>
       </c>
       <c r="R117" t="n">
-        <v>7302956</v>
+        <v>7303094</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13165,6 +13161,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>19 stänglar</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13179,12 +13180,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -13195,10 +13196,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118640728</v>
+        <v>118640707</v>
       </c>
       <c r="B118" t="n">
-        <v>77875</v>
+        <v>96814</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13207,25 +13208,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6437</v>
+        <v>221941</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13235,10 +13236,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>715229</v>
+        <v>715323</v>
       </c>
       <c r="R118" t="n">
-        <v>7302995</v>
+        <v>7303053</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13301,10 +13302,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118638455</v>
+        <v>118631176</v>
       </c>
       <c r="B119" t="n">
-        <v>78491</v>
+        <v>97874</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13313,41 +13314,41 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Slaktarberget, Pi lm</t>
+          <t>Slaktarberget (Slaktarberget), Pi lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>715199</v>
+        <v>715553</v>
       </c>
       <c r="R119" t="n">
-        <v>7303011</v>
+        <v>7303155</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13374,9 +13375,19 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13391,26 +13402,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118641450</v>
+        <v>118641310</v>
       </c>
       <c r="B120" t="n">
-        <v>90476</v>
+        <v>97874</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13423,34 +13430,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>715402</v>
+        <v>715194</v>
       </c>
       <c r="R120" t="n">
-        <v>7302984</v>
+        <v>7303422</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13480,43 +13495,50 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118638434</v>
+        <v>118640704</v>
       </c>
       <c r="B121" t="n">
-        <v>90476</v>
+        <v>79080</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13525,25 +13547,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13553,13 +13575,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>715541</v>
+        <v>715432</v>
       </c>
       <c r="R121" t="n">
-        <v>7303144</v>
+        <v>7302962</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13603,22 +13625,26 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr"/>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118642115</v>
+        <v>118642118</v>
       </c>
       <c r="B122" t="n">
-        <v>97874</v>
+        <v>78228</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13627,25 +13653,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13655,10 +13681,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>715580</v>
+        <v>715332</v>
       </c>
       <c r="R122" t="n">
-        <v>7303094</v>
+        <v>7303306</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13691,11 +13717,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>19 stänglar</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13726,10 +13747,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118640707</v>
+        <v>118637558</v>
       </c>
       <c r="B123" t="n">
-        <v>96814</v>
+        <v>78228</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13738,25 +13759,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221941</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13766,13 +13787,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>715323</v>
+        <v>715556</v>
       </c>
       <c r="R123" t="n">
-        <v>7303053</v>
+        <v>7303103</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13816,12 +13837,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13832,10 +13853,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118631176</v>
+        <v>118638453</v>
       </c>
       <c r="B124" t="n">
-        <v>97874</v>
+        <v>78491</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13844,41 +13865,41 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Slaktarberget (Slaktarberget), Pi lm</t>
+          <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>715553</v>
+        <v>715390</v>
       </c>
       <c r="R124" t="n">
-        <v>7303155</v>
+        <v>7302980</v>
       </c>
       <c r="S124" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13905,19 +13926,9 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13932,22 +13943,26 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118641310</v>
+        <v>118639962</v>
       </c>
       <c r="B125" t="n">
-        <v>97874</v>
+        <v>78491</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13956,49 +13971,41 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>715194</v>
+        <v>715598</v>
       </c>
       <c r="R125" t="n">
-        <v>7303422</v>
+        <v>7302991</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14025,50 +14032,43 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr"/>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118642118</v>
+        <v>118640708</v>
       </c>
       <c r="B126" t="n">
-        <v>78228</v>
+        <v>78517</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14077,25 +14077,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14105,13 +14105,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>715332</v>
+        <v>715178</v>
       </c>
       <c r="R126" t="n">
-        <v>7303306</v>
+        <v>7302956</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14155,12 +14155,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -14171,10 +14171,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118637558</v>
+        <v>118640728</v>
       </c>
       <c r="B127" t="n">
-        <v>78228</v>
+        <v>77875</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14187,21 +14187,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14211,13 +14211,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>715556</v>
+        <v>715229</v>
       </c>
       <c r="R127" t="n">
-        <v>7303103</v>
+        <v>7302995</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14261,12 +14261,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -14277,10 +14277,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118640704</v>
+        <v>118638455</v>
       </c>
       <c r="B128" t="n">
-        <v>79080</v>
+        <v>78491</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14293,21 +14293,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14317,13 +14317,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>715432</v>
+        <v>715199</v>
       </c>
       <c r="R128" t="n">
-        <v>7302962</v>
+        <v>7303011</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14367,12 +14367,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -15448,10 +15448,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118641466</v>
+        <v>118639261</v>
       </c>
       <c r="B139" t="n">
-        <v>78491</v>
+        <v>78573</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15464,37 +15464,40 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>715566</v>
+        <v>715520</v>
       </c>
       <c r="R139" t="n">
-        <v>7303083</v>
+        <v>7303163</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15532,18 +15535,19 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -15554,10 +15558,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118640959</v>
+        <v>118637517</v>
       </c>
       <c r="B140" t="n">
-        <v>78491</v>
+        <v>91203</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15566,41 +15570,38 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>715559</v>
+        <v>715427</v>
       </c>
       <c r="R140" t="n">
-        <v>7303088</v>
+        <v>7303025</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15641,29 +15642,32 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY140" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118637576</v>
+        <v>118639970</v>
       </c>
       <c r="B141" t="n">
-        <v>78491</v>
+        <v>91786</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15672,25 +15676,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15700,13 +15704,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>715542</v>
+        <v>715124</v>
       </c>
       <c r="R141" t="n">
-        <v>7303078</v>
+        <v>7302952</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15750,12 +15754,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15766,10 +15770,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118638461</v>
+        <v>118639946</v>
       </c>
       <c r="B142" t="n">
-        <v>90476</v>
+        <v>79600</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15782,21 +15786,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15806,13 +15810,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>715146</v>
+        <v>715150</v>
       </c>
       <c r="R142" t="n">
-        <v>7302931</v>
+        <v>7302968</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15856,12 +15860,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15872,10 +15876,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118637533</v>
+        <v>118641466</v>
       </c>
       <c r="B143" t="n">
-        <v>97874</v>
+        <v>78491</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15884,25 +15888,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15912,10 +15916,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>715519</v>
+        <v>715566</v>
       </c>
       <c r="R143" t="n">
-        <v>7303000</v>
+        <v>7303083</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15956,19 +15960,18 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -15979,10 +15982,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118640712</v>
+        <v>118640959</v>
       </c>
       <c r="B144" t="n">
-        <v>78228</v>
+        <v>78491</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15995,37 +15998,40 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>715327</v>
+        <v>715559</v>
       </c>
       <c r="R144" t="n">
-        <v>7303326</v>
+        <v>7303088</v>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16063,32 +16069,29 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118639261</v>
+        <v>118637576</v>
       </c>
       <c r="B145" t="n">
-        <v>78573</v>
+        <v>78491</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16101,40 +16104,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>715520</v>
+        <v>715542</v>
       </c>
       <c r="R145" t="n">
-        <v>7303163</v>
+        <v>7303078</v>
       </c>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16172,19 +16172,18 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -16195,10 +16194,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118637517</v>
+        <v>118638461</v>
       </c>
       <c r="B146" t="n">
-        <v>91203</v>
+        <v>90476</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16211,21 +16210,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16235,10 +16234,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>715427</v>
+        <v>715146</v>
       </c>
       <c r="R146" t="n">
-        <v>7303025</v>
+        <v>7302931</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16285,12 +16284,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -16301,10 +16300,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118639970</v>
+        <v>118641087</v>
       </c>
       <c r="B147" t="n">
-        <v>91786</v>
+        <v>57401</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16317,24 +16316,32 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
@@ -16344,10 +16351,10 @@
         <v>715124</v>
       </c>
       <c r="R147" t="n">
-        <v>7302952</v>
+        <v>7302962</v>
       </c>
       <c r="S147" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16374,9 +16381,19 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16391,26 +16408,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
-        </is>
-      </c>
-      <c r="AY147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118639946</v>
+        <v>118637533</v>
       </c>
       <c r="B148" t="n">
-        <v>79600</v>
+        <v>97874</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16423,21 +16436,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16447,13 +16460,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>715150</v>
+        <v>715519</v>
       </c>
       <c r="R148" t="n">
-        <v>7302968</v>
+        <v>7303000</v>
       </c>
       <c r="S148" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16491,18 +16504,19 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -16513,10 +16527,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118641087</v>
+        <v>118640712</v>
       </c>
       <c r="B149" t="n">
-        <v>57401</v>
+        <v>78228</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16525,49 +16539,41 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>715124</v>
+        <v>715327</v>
       </c>
       <c r="R149" t="n">
-        <v>7302962</v>
+        <v>7303326</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16594,19 +16600,9 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16621,22 +16617,26 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr"/>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118639952</v>
+        <v>118639937</v>
       </c>
       <c r="B150" t="n">
-        <v>90525</v>
+        <v>97874</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16645,25 +16645,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1204</v>
+        <v>221952</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16673,10 +16673,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>715088</v>
+        <v>715562</v>
       </c>
       <c r="R150" t="n">
-        <v>7302934</v>
+        <v>7303104</v>
       </c>
       <c r="S150" t="n">
         <v>1</v>
@@ -17061,10 +17061,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118639937</v>
+        <v>118640698</v>
       </c>
       <c r="B154" t="n">
-        <v>97874</v>
+        <v>79109</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17073,25 +17073,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17101,13 +17101,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>715562</v>
+        <v>715185</v>
       </c>
       <c r="R154" t="n">
-        <v>7303104</v>
+        <v>7302968</v>
       </c>
       <c r="S154" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -17167,7 +17167,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118640698</v>
+        <v>118640693</v>
       </c>
       <c r="B155" t="n">
         <v>79109</v>
@@ -17207,10 +17207,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>715185</v>
+        <v>715329</v>
       </c>
       <c r="R155" t="n">
-        <v>7302968</v>
+        <v>7303326</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -17273,10 +17273,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>118640693</v>
+        <v>118639952</v>
       </c>
       <c r="B156" t="n">
-        <v>79109</v>
+        <v>90525</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17289,21 +17289,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17313,13 +17313,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>715329</v>
+        <v>715088</v>
       </c>
       <c r="R156" t="n">
-        <v>7303326</v>
+        <v>7302934</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17363,12 +17363,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -17379,10 +17379,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118640721</v>
+        <v>118642117</v>
       </c>
       <c r="B157" t="n">
-        <v>78573</v>
+        <v>57306</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17395,37 +17395,45 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>715534</v>
+        <v>715634</v>
       </c>
       <c r="R157" t="n">
-        <v>7303166</v>
+        <v>7303012</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17455,6 +17463,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17469,12 +17482,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -17485,10 +17498,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118639953</v>
+        <v>118640721</v>
       </c>
       <c r="B158" t="n">
-        <v>90661</v>
+        <v>78573</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17497,25 +17510,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1503</v>
+        <v>864</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17525,13 +17538,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>715480</v>
+        <v>715534</v>
       </c>
       <c r="R158" t="n">
-        <v>7302982</v>
+        <v>7303166</v>
       </c>
       <c r="S158" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17575,12 +17588,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -17591,10 +17604,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118640722</v>
+        <v>118639953</v>
       </c>
       <c r="B159" t="n">
-        <v>78491</v>
+        <v>90661</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17603,25 +17616,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17631,13 +17644,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>715522</v>
+        <v>715480</v>
       </c>
       <c r="R159" t="n">
-        <v>7303150</v>
+        <v>7302982</v>
       </c>
       <c r="S159" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17681,12 +17694,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -17697,10 +17710,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>118642117</v>
+        <v>118640722</v>
       </c>
       <c r="B160" t="n">
-        <v>57306</v>
+        <v>78491</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17713,45 +17726,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>715634</v>
+        <v>715522</v>
       </c>
       <c r="R160" t="n">
-        <v>7303012</v>
+        <v>7303150</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17781,11 +17786,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>hack</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17800,12 +17800,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -20957,10 +20957,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>118641461</v>
+        <v>118640738</v>
       </c>
       <c r="B190" t="n">
-        <v>96814</v>
+        <v>79572</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20969,25 +20969,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20997,10 +20997,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>715070</v>
+        <v>715305</v>
       </c>
       <c r="R190" t="n">
-        <v>7302926</v>
+        <v>7302918</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21047,12 +21047,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -21063,10 +21063,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>118642112</v>
+        <v>118641461</v>
       </c>
       <c r="B191" t="n">
-        <v>97874</v>
+        <v>96814</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21079,21 +21079,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21103,10 +21103,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>715577</v>
+        <v>715070</v>
       </c>
       <c r="R191" t="n">
-        <v>7303094</v>
+        <v>7302926</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21141,11 +21141,6 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>30 stänglar</t>
-        </is>
-      </c>
       <c r="AD191" t="b">
         <v>0</v>
       </c>
@@ -21158,12 +21153,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -21174,7 +21169,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>118639936</v>
+        <v>118642112</v>
       </c>
       <c r="B192" t="n">
         <v>97874</v>
@@ -21214,13 +21209,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>715328</v>
+        <v>715577</v>
       </c>
       <c r="R192" t="n">
-        <v>7303394</v>
+        <v>7303094</v>
       </c>
       <c r="S192" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21250,6 +21245,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>30 stänglar</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21264,12 +21264,12 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -21280,10 +21280,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>118639919</v>
+        <v>118639936</v>
       </c>
       <c r="B193" t="n">
-        <v>104932</v>
+        <v>97874</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21296,21 +21296,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21320,10 +21320,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>715338</v>
+        <v>715328</v>
       </c>
       <c r="R193" t="n">
-        <v>7303350</v>
+        <v>7303394</v>
       </c>
       <c r="S193" t="n">
         <v>1</v>
@@ -21386,10 +21386,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>118640738</v>
+        <v>118639919</v>
       </c>
       <c r="B194" t="n">
-        <v>79572</v>
+        <v>104932</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21398,25 +21398,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21426,13 +21426,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>715305</v>
+        <v>715338</v>
       </c>
       <c r="R194" t="n">
-        <v>7302918</v>
+        <v>7303350</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -21476,12 +21476,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -22022,10 +22022,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>118642123</v>
+        <v>118640760</v>
       </c>
       <c r="B200" t="n">
-        <v>5166</v>
+        <v>78227</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22034,25 +22034,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100526</v>
+        <v>6446</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22062,10 +22062,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>715473</v>
+        <v>715315</v>
       </c>
       <c r="R200" t="n">
-        <v>7302975</v>
+        <v>7302930</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22112,12 +22112,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -22128,10 +22128,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>118640754</v>
+        <v>118639057</v>
       </c>
       <c r="B201" t="n">
-        <v>57443</v>
+        <v>74603</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22144,37 +22144,40 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>715572</v>
+        <v>715250</v>
       </c>
       <c r="R201" t="n">
-        <v>7303153</v>
+        <v>7303027</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22206,29 +22209,25 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Sång av talltita</t>
-        </is>
-      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
       <c r="AE201" t="b">
         <v>0</v>
       </c>
+      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -22239,10 +22238,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>118640760</v>
+        <v>118642123</v>
       </c>
       <c r="B202" t="n">
-        <v>78227</v>
+        <v>5166</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22251,25 +22250,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6446</v>
+        <v>100526</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22279,10 +22278,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>715315</v>
+        <v>715473</v>
       </c>
       <c r="R202" t="n">
-        <v>7302930</v>
+        <v>7302975</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22329,12 +22328,12 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -22345,10 +22344,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>118639057</v>
+        <v>118640754</v>
       </c>
       <c r="B203" t="n">
-        <v>74603</v>
+        <v>57443</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22361,40 +22360,37 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>715250</v>
+        <v>715572</v>
       </c>
       <c r="R203" t="n">
-        <v>7303027</v>
+        <v>7303153</v>
       </c>
       <c r="S203" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22426,25 +22422,29 @@
           <t>2024-07-23</t>
         </is>
       </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Sång av talltita</t>
+        </is>
+      </c>
       <c r="AD203" t="b">
         <v>0</v>
       </c>
       <c r="AE203" t="b">
         <v>0</v>
       </c>
-      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
@@ -22455,10 +22455,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>118637532</v>
+        <v>118638441</v>
       </c>
       <c r="B204" t="n">
-        <v>90458</v>
+        <v>78228</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22471,21 +22471,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>112</v>
+        <v>228912</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22495,10 +22495,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>715538</v>
+        <v>715326</v>
       </c>
       <c r="R204" t="n">
-        <v>7303146</v>
+        <v>7303317</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22545,12 +22545,12 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
@@ -22561,10 +22561,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>118637584</v>
+        <v>118641454</v>
       </c>
       <c r="B205" t="n">
-        <v>90756</v>
+        <v>79080</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22573,25 +22573,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22601,10 +22601,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>715318</v>
+        <v>715510</v>
       </c>
       <c r="R205" t="n">
-        <v>7303032</v>
+        <v>7302988</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22651,12 +22651,12 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
@@ -23101,10 +23101,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>118640835</v>
+        <v>118637532</v>
       </c>
       <c r="B210" t="n">
-        <v>78491</v>
+        <v>90458</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23117,37 +23117,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>715308</v>
+        <v>715538</v>
       </c>
       <c r="R210" t="n">
-        <v>7303003</v>
+        <v>7303146</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23188,29 +23185,32 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY210" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>118639939</v>
+        <v>118637584</v>
       </c>
       <c r="B211" t="n">
-        <v>57306</v>
+        <v>90756</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -23219,25 +23219,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100049</v>
+        <v>65</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23247,13 +23247,13 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>715163</v>
+        <v>715318</v>
       </c>
       <c r="R211" t="n">
-        <v>7303461</v>
+        <v>7303032</v>
       </c>
       <c r="S211" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -23283,11 +23283,6 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23302,12 +23297,12 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
@@ -23318,10 +23313,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>118640720</v>
+        <v>118640835</v>
       </c>
       <c r="B212" t="n">
-        <v>78227</v>
+        <v>78491</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23334,37 +23329,40 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>715120</v>
+        <v>715308</v>
       </c>
       <c r="R212" t="n">
-        <v>7302906</v>
+        <v>7303003</v>
       </c>
       <c r="S212" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -23402,32 +23400,29 @@
       <c r="AE212" t="b">
         <v>0</v>
       </c>
+      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
-        </is>
-      </c>
-      <c r="AY212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>118641454</v>
+        <v>118639939</v>
       </c>
       <c r="B213" t="n">
-        <v>79080</v>
+        <v>57306</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -23440,21 +23435,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23464,13 +23459,13 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>715510</v>
+        <v>715163</v>
       </c>
       <c r="R213" t="n">
-        <v>7302988</v>
+        <v>7303461</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23500,6 +23495,11 @@
       <c r="AA213" t="inlineStr">
         <is>
           <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23514,12 +23514,12 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
@@ -23530,10 +23530,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>118638441</v>
+        <v>118640720</v>
       </c>
       <c r="B214" t="n">
-        <v>78228</v>
+        <v>78227</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23546,21 +23546,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -23570,13 +23570,13 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>715326</v>
+        <v>715120</v>
       </c>
       <c r="R214" t="n">
-        <v>7303317</v>
+        <v>7302906</v>
       </c>
       <c r="S214" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -23620,12 +23620,12 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
@@ -25666,10 +25666,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>118638454</v>
+        <v>118638435</v>
       </c>
       <c r="B234" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -25682,21 +25682,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -25706,10 +25706,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>715351</v>
+        <v>715205</v>
       </c>
       <c r="R234" t="n">
-        <v>7302999</v>
+        <v>7303041</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25764,15 +25764,11 @@
           <t>Petra Wikström</t>
         </is>
       </c>
-      <c r="AY234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>118640732</v>
+        <v>118638454</v>
       </c>
       <c r="B235" t="n">
         <v>78491</v>
@@ -25806,19 +25802,16 @@
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>715236</v>
+        <v>715351</v>
       </c>
       <c r="R235" t="n">
-        <v>7302978</v>
+        <v>7302999</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25859,29 +25852,32 @@
       <c r="AE235" t="b">
         <v>0</v>
       </c>
-      <c r="AF235" t="inlineStr"/>
       <c r="AG235" t="b">
         <v>0</v>
       </c>
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY235" t="inlineStr"/>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>118638435</v>
+        <v>118640732</v>
       </c>
       <c r="B236" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25894,34 +25890,37 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Slaktarberget, Pi lm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>715205</v>
+        <v>715236</v>
       </c>
       <c r="R236" t="n">
-        <v>7303041</v>
+        <v>7302978</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25962,18 +25961,19 @@
       <c r="AE236" t="b">
         <v>0</v>
       </c>
+      <c r="AF236" t="inlineStr"/>
       <c r="AG236" t="b">
         <v>0</v>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>

--- a/artfynd/A 29088-2023 artfynd.xlsx
+++ b/artfynd/A 29088-2023 artfynd.xlsx
@@ -6891,11 +6891,11 @@
         <v>118639925</v>
       </c>
       <c r="B59" t="n">
-        <v>56504</v>
+        <v>56687</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">

--- a/artfynd/A 29088-2023 artfynd.xlsx
+++ b/artfynd/A 29088-2023 artfynd.xlsx
@@ -6891,7 +6891,7 @@
         <v>118639925</v>
       </c>
       <c r="B59" t="n">
-        <v>56687</v>
+        <v>56688</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>

--- a/artfynd/A 29088-2023 artfynd.xlsx
+++ b/artfynd/A 29088-2023 artfynd.xlsx
@@ -6891,7 +6891,7 @@
         <v>118639925</v>
       </c>
       <c r="B59" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
